--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-07.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-07.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583987025402</v>
+        <v>5583988266369</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Addissana</t>
+          <t>Construtora</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Addissana de Carvalho</t>
+          <t>Construtora Britales</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583993956136</v>
+        <v>5583987967522</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Mikael</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maria do Socorro da Silva</t>
+          <t>Mikael Patrick Soares Souza e Silva</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583988333333</v>
+        <v>5583996612472</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ney</t>
+          <t>Giancarlos</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ney Walter Almeida</t>
+          <t>Giancarlos Tavares de Moura</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583998735855</v>
+        <v>5583987025402</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Addissana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Douglas Andrade de Meneses</t>
+          <t>Addissana de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5563984231822</v>
+        <v>5583993956136</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Isabel</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Isabel Cristina Albuquerque Leite</t>
+          <t>Maria do Socorro da Silva</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583991888779</v>
+        <v>5583988333333</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maanain</t>
+          <t>Ney</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Maanain Residence</t>
+          <t>Ney Walter Almeida</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583988709602</v>
+        <v>5583998735855</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Daise</t>
+          <t>Douglas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Daise Souto da Silva</t>
+          <t>Douglas Andrade de Meneses</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583996541507</v>
+        <v>5563984231822</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Philipe</t>
+          <t>Isabel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philipe Alexandre Souza Santos</t>
+          <t>Isabel Cristina Albuquerque Leite</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583987860476</v>
+        <v>5583991888779</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Juliene</t>
+          <t>Maanain</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Juliene Hosana Silva Morais</t>
+          <t>Maanain Residence</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583988096018</v>
+        <v>5583988709602</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lemaq</t>
+          <t>Daise</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lemaq Maquinas e Ferramentas</t>
+          <t>Daise Souto da Silva</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583987168137</v>
+        <v>5583996541507</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Higor</t>
+          <t>Philipe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Higor Marques Vieira Sousa</t>
+          <t>Philipe Alexandre Souza Santos</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583988373655</v>
+        <v>5583987860476</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Juliene</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Antonio Cassemiro de Sousa</t>
+          <t>Juliene Hosana Silva Morais</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583999291993</v>
+        <v>5583988096018</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vigor</t>
+          <t>Lemaq</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vigor da Paz</t>
+          <t>Lemaq Maquinas e Ferramentas</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583991493995</v>
+        <v>5583987168137</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thayse</t>
+          <t>Higor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thayse do Nascimento da Silva</t>
+          <t>Higor Marques Vieira Sousa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583987616953</v>
+        <v>5583988373655</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Josefa</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Josefa Idalina de Sousa</t>
+          <t>Antonio Cassemiro de Sousa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583988638302</v>
+        <v>5583999291993</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Vigor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Thiago de Araujo Trajano</t>
+          <t>Vigor da Paz</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583988995271</v>
+        <v>5583991493995</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Josenildo</t>
+          <t>Thayse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Josenildo de Almeida Carneiro</t>
+          <t>Thayse do Nascimento da Silva</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583996960983</v>
+        <v>5583987616953</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rodrigo</t>
+          <t>Josefa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rodrigo Silva do Nascimento</t>
+          <t>Josefa Idalina de Sousa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583981603495</v>
+        <v>5583988638302</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Antonio Marcos dos Santos Alves</t>
+          <t>Luis Thiago de Araujo Trajano</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5561984234518</v>
+        <v>5583988995271</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Josenildo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nelson da Silva Novais</t>
+          <t>Josenildo de Almeida Carneiro</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583988124082</v>
+        <v>5583996960983</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Luzicleide</t>
+          <t>Rodrigo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Luzicleide Oliveira Dias</t>
+          <t>Rodrigo Silva do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583991416693</v>
+        <v>5583981603495</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Renan</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Renan Lavor Martins de Souza</t>
+          <t>Antonio Marcos dos Santos Alves</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5521986452449</v>
+        <v>5561984234518</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Diaogo</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Diaogo Santos de Oliveira Prado</t>
+          <t>Nelson da Silva Novais</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583991873614</v>
+        <v>5583988124082</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Luzicleide</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Carlos Antonio de Azevedo</t>
+          <t>Luzicleide Oliveira Dias</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583987412906</v>
+        <v>5583991416693</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Renan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Williams Lopes Costa</t>
+          <t>Renan Lavor Martins de Souza</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583981309134</v>
+        <v>5521986452449</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alessandra</t>
+          <t>Diaogo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alessandra Trajano</t>
+          <t>Diaogo Santos de Oliveira Prado</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583993517527</v>
+        <v>5583991873614</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alexandre Andrade Ferreira</t>
+          <t>Carlos Antonio de Azevedo</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583996769246</v>
+        <v>5583987412906</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ijeval</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ijeval Rodrigues Coelho</t>
+          <t>Williams Lopes Costa</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583999843862</v>
+        <v>5583981309134</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nereide</t>
+          <t>Alessandra</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nereide de Andrade Virginio Silva</t>
+          <t>Alessandra Trajano</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583993094119</v>
+        <v>5583993517527</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Joao Paulo Martins</t>
+          <t>Alexandre Andrade Ferreira</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583996837860</v>
+        <v>5583996769246</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Joas</t>
+          <t>Ijeval</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Joas Alberto da Silva</t>
+          <t>Ijeval Rodrigues Coelho</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5584998079242</v>
+        <v>5583999843862</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Nereide</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Daniel Gomes Ferreira</t>
+          <t>Nereide de Andrade Virginio Silva</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583994187885</v>
+        <v>5583993094119</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Phodium</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phodium Soluções</t>
+          <t>Joao Paulo Martins</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583986995230</v>
+        <v>5583996837860</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Madalena</t>
+          <t>Joas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Madalena Maria Almeida Barreto</t>
+          <t>Joas Alberto da Silva</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583999171730</v>
+        <v>5584998079242</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Danilo Henrique da Costa Silva</t>
+          <t>Daniel Gomes Ferreira</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583981169823</v>
+        <v>5583994187885</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Phodium</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Danielle Rossato</t>
+          <t>Phodium Soluções</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5581992991495</v>
+        <v>5583986995230</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Janaina</t>
+          <t>Madalena</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Janaina da Silva Lima</t>
+          <t>Madalena Maria Almeida Barreto</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583991436026</v>
+        <v>5583999171730</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jorge da Silva Gusmao</t>
+          <t>Danilo Henrique da Costa Silva</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583999432856</v>
+        <v>5583981169823</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Antonio Francisco de Paulo Neto</t>
+          <t>Danielle Rossato</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583996246201</v>
+        <v>5581992991495</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Luciano</t>
+          <t>Janaina</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Luciano de Lima</t>
+          <t>Janaina da Silva Lima</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583993513535</v>
+        <v>5583991436026</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Antonio Guilherme Alencar Nelo</t>
+          <t>Jorge da Silva Gusmao</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583999043271</v>
+        <v>5583999432856</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Halisson</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Halisson da Silva</t>
+          <t>Antonio Francisco de Paulo Neto</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583988362998</v>
+        <v>5583996246201</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Luciano</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Maria Edna de Melo</t>
+          <t>Luciano de Lima</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583988356795</v>
+        <v>5583993513535</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marcilio</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marcilio Cesar de Macedo Nunes</t>
+          <t>Antonio Guilherme Alencar Nelo</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583988823307</v>
+        <v>5583999043271</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Halisson</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jose Lucio da Costa</t>
+          <t>Halisson da Silva</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583988942020</v>
+        <v>5583988362998</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vanessa Pereira</t>
+          <t>Maria Edna de Melo</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5547997189049</v>
+        <v>5583988356795</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cibela</t>
+          <t>Marcilio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cibela Rebeca Fernandes Bento</t>
+          <t>Marcilio Cesar de Macedo Nunes</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583999695161</v>
+        <v>5583988823307</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Amanda Leticia Franca da Silva</t>
+          <t>Jose Lucio da Costa</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583999617935</v>
+        <v>5583988942020</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ednado</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ednado de Araujo Pereira</t>
+          <t>Vanessa Pereira</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583998818221</v>
+        <v>5547997189049</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>João</t>
+          <t>Cibela</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>João Carlos Borges Correia de Aguiar</t>
+          <t>Cibela Rebeca Fernandes Bento</t>
         </is>
       </c>
     </row>
